--- a/PTBR/Lang/PTBR/Dialog/Drama/guild_master_merchant.xlsx
+++ b/PTBR/Lang/PTBR/Dialog/Drama/guild_master_merchant.xlsx
@@ -629,7 +629,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Como está indo minha tarefa para você? Espero que não esteja se atrevendo a procrastinar sob minha supervisão.  </t>
+          <t>Como está indo a minha tarefa? Espero que não esteja ousando enrolar na minha vigília.</t>
         </is>
       </c>
     </row>
@@ -672,9 +672,9 @@
           <t>Well, well, what's the matter? Can't you see I'm swamped? Out with it.</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Muito bem, muito bem, qual é o problema? Não vê que estou atarefado? Diga logo.  </t>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>Pois é, que foi? Não vê que estou atolada? Fala logo.</t>
         </is>
       </c>
     </row>
@@ -707,9 +707,9 @@
           <t>I want to join the Merchants Guild.</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Quero entrar para a Guilda dos Mercadores.  </t>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>Quero entrar na Guilda dos Mercadores.</t>
         </is>
       </c>
     </row>
@@ -763,11 +763,10 @@
 Any proper merchant knows they can join my guild without conditions. Yet here you stand, dressed like a ragged adventurer. Are you certain you belong with us?</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Oh? Você deseja entrar para a minha Guilda dos Mercadores?  _x000D_
-_x000D_
-Qualquer comerciante de verdade sabe que pode se juntar à minha guilda sem condições. No entanto, aqui está você, vestido como um aventureiro esfarrapado. Tem certeza de que pertence a nós?  </t>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>Oh? quer entrar na minha Guilda dos Mercadores?
+Todo mercador decente sabe que pode entrar na minha guilda sem condições. Mas aqui está você, vestido como um aventureiro esfarrapado. Tem certeza de que pertence ao nosso meio?</t>
         </is>
       </c>
     </row>
@@ -785,9 +784,9 @@
           <t>Ha, intriguing. I quite fancy that defiant look of yours. Very well. I, Lady Marian, shall personally administer your test.</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ha, intrigante. Gosto bastante desse seu olhar desafiador. Muito bem. Eu, Lady Marian, pessoalmente administrarei seu teste.  </t>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>Ha, intrigante. Gosto desse seu olhar desafiador. Muito bem. Eu, Lady Marian, pessoalmente aplicarei sua prova.</t>
         </is>
       </c>
     </row>
@@ -805,9 +804,9 @@
           <t>Let's see...I'll have you distribute flyers for your initiation. Purchase a good amount of flyers from our guild clerk and hand them out in some town.</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vejamos... Você distribuirá panfletos como parte de sua iniciação. Compre uma boa quantidade de panfletos com o atendente da guilda e distribua-os em alguma cidade.  </t>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>Vejamos...você vai distribuir panfletos como iniciação. Compre uma boa quantidade de panfletos com o escrivão da guilda e distribua numa cidade.</t>
         </is>
       </c>
     </row>
@@ -843,13 +842,11 @@
 Off you go! Show the world the spirit of a merchant!</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Um conselho meu para um novato como você.  _x000D_
-_x000D_
-Não distribua esses panfletos de qualquer jeito. Fique firme no meio da multidão e espalhe-os com toda a paixão que arde dentro de você.  _x000D_
-_x000D_
-Lá vai você! Mostre ao mundo o espírito de um comerciante!</t>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>Uma dose de sabedoria minha para um novato como você.
+Não entregue os panfletos escondido. Fique orgulhoso no meio da multidão e lance-os com toda a paixão que arde em você.
+Anda logo! Mostre ao mundo o espírito de um mercador!</t>
         </is>
       </c>
     </row>
@@ -887,11 +884,10 @@
 Fine. I shall formally recognize you as a member of my Merchants Guild. </t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Muito bem, muito bem, terminou com os panfletos, foi? Seu fervor pelo comércio parece genuíno.  _x000D_
-_x000D_
-Certo. Eu o reconhecerei formalmente como um membro da minha Guilda dos Mercadores.  </t>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pois é, terminou os panfletos, terminou? Sua paixão pelo comércio parece genuína.
+Certo. Vou reconhecê-lo formalmente como membro da minha Guilda dos Mercadores. </t>
         </is>
       </c>
     </row>
@@ -924,11 +920,10 @@
 Know that the world of commerce is a ruthless arena, teeming with demons ready to balance your very soul against their gold. Let down your guard, and they'll devour you.</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">E tire esse ar convencido do rosto. Entrar na guilda não é um passe para a complacência.  _x000D_
-_x000D_
-Saiba que o mundo do comércio é uma arena implacável, repleta de demônios prontos para trocar sua própria alma por ouro. Baixe a guarda, e eles o devorarão.  </t>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>E apague essa cara de satisfeito. Entrar na guilda não é passaporte para acomodação.
+Saiba que o mundo do comércio é uma arena impiedosa, fervendo de demônios prontos para apostar sua alma no ouro deles. Baixar a guarda, e eles devoram você.</t>
         </is>
       </c>
     </row>
@@ -946,9 +941,9 @@
           <t>Ha, don't get too scared. You are a merchant recognized by Lady Marian. I eagerly anticipate the day your name strikes fear and respect amidst the titans of commerce.</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ha, não se assuste tanto. Você agora é um comerciante reconhecido por Lady Marian. Aguardo ansiosamente o dia em que seu nome inspirará medo e respeito entre os titãs do comércio."  </t>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>Ha, não fique com medo demais. Você é um mercador reconhecido pela Lady Marian. Aguardo com ansiedade o dia em que seu nome espalhar medo e respeito entre os gigantes do comércio.</t>
         </is>
       </c>
     </row>
